--- a/sample_data/검증포인트_참고용.xlsx
+++ b/sample_data/검증포인트_참고용.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -473,7 +473,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>정상 케이스 - 외환차익 250,000원 정확히 계상됨</t>
+          <t>정상 케이스 - 실제 환율 그대로 정확히 계상됨(외환차손 161,000원, USD 하락)</t>
         </is>
       </c>
     </row>
@@ -495,7 +495,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>오류 케이스 - 결제일 실제 환율이 아닌 전월말 환율을 잘못 적용</t>
+          <t>오류 케이스 - 결제일 실제 환율(1415.80)이 아닌 전월말 환율(1438.50)을 잘못 적용. 실제 데이터 기준 괴리율은 1.6%로 5% 개별기준은 통과하지만, 합계중요성에서 걸림</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>오류 케이스 - 외환차익 100,000원을 별도 계정으로 인식하지 않고 채권 계정에서 바로 상계(외환차익 계상 누락)</t>
+          <t>오류 케이스 - 환율 자체는 실제값을 정확히 썼지만, 외환차익 90,000원을 별도 계정으로 인식하지 않고 채권 계정에서 바로 상계(외환차익 계상 누락). 괴리율 0%라 1단계에선 안 걸리고 합계중요성에서 걸리는 케이스</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>정상 케이스 - 외환차손 45,000원 정확히 계상됨(부채, 환율상승=손실)</t>
+          <t>정상 케이스 - 실제 환율 그대로 정확히 계상됨(외환차익 103,500원, EUR 하락으로 부채 상환액 감소)</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>정상 케이스 - 기말 미결제, 기말환율로 정확히 재평가(외화환산이익 200,000원)</t>
+          <t>정상 케이스 - 기말 미결제, 실제 결산일 환율로 정확히 재평가(외화환산손실 22,400원)</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>기말 미실현(외화환산)</t>
+          <t>실현(결제완료)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -627,34 +627,166 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>오류 케이스 - 기말 재평가 시 당기말 환율이 아닌 전기말 환율을 잘못 사용 (방향까지 반대로 계상)</t>
+          <t>오류 케이스 - 기말 재평가 시 당기말 환율(1434.90)이 아닌 전기말 환율(1470.00)을 잘못 사용해 외화환산이익을 과대계상(1,159,500원 vs 정상 633,000원)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TXN009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>실현(결제완료)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>정상 케이스 - GBP, 한 거래를 두 번(2025-03-10 / 2025-05-20)에 나눠 결제했고 각 회차 모두 실제 환율대로 정확히 반영됨(분할결제 처리 검증용)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>계정별원장 관련 별도 이슈</t>
+          <t>TXN010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>기말 미실현(외화환산)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>정상 케이스 - HKD, 기말 미결제 상태에서 실제 결산일 환율로 정확히 재평가됨(신규 통화 HKD 검증용)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>TXN011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>실현(결제완료)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>정상 케이스 - CHF, 1차 스크리닝에서는 매매기준율 대비 괴리가 커서(약 8%) 이상치로 걸리지만, 실제로는 은행 전신환매매율(우대환율)을 정상 적용한 것으로 2단계 증빙 OCR을 통해 적정으로 확인됨(false positive가 해소되는 사례)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TXN012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>실현(결제완료)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>정상 케이스 - CAD, 실제 환율 그대로 정확히 계상됨(신규 통화 CAD 검증용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TXN013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>실현(결제완료)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>오류</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>오류 케이스 - AUD, 결제 시 실제 환율(918.75)이 아닌 잘못된 환율(980.00)을 적용했고, 2단계 증빙(은행 외환거래확인서) OCR로도 불일치가 재확인됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TXN014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>기말 미실현(외화환산)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>정상 케이스 - SGD, 기말 미결제 상태에서 실제 결산일 환율로 정확히 재평가됨(신규 통화 SGD 검증용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>계정별원장 관련 별도 이슈</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>907 외환차익 계정</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>오류</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>계정별원장 기말잔액이 분개장 합계보다 50,000원 많음(상위 시스템 수기조정분 미반영 가정) - 3개 문서 교차검증 필요성을 보여주는 케이스</t>
         </is>
